--- a/zib2017-2020/mapping deprecated zibs/deprecated_zib_versions.xlsx
+++ b/zib2017-2020/mapping deprecated zibs/deprecated_zib_versions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nictiznl-my.sharepoint.com/personal/wouter_zanen_nictiz_nl/Documents/Documenten/GitHub/Zibtranslate/zib2017-2020/mapping deprecated zibs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{388C1A51-1026-0E49-B90D-AE64119FA45A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D588971D-FD11-4513-B54C-6E12AFAAA180}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{388C1A51-1026-0E49-B90D-AE64119FA45A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C01148C-19BC-4D74-99CB-CFFD9A96813F}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{6A031DF4-A5D7-7D41-A8E4-057E405138E6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{6A031DF4-A5D7-7D41-A8E4-057E405138E6}"/>
   </bookViews>
   <sheets>
     <sheet name="table_info_zibs" sheetId="8" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2398" uniqueCount="612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2400" uniqueCount="615">
   <si>
     <t>zib</t>
   </si>
@@ -1878,6 +1878,15 @@
   </si>
   <si>
     <t>OID_zib2020</t>
+  </si>
+  <si>
+    <t>zib2017</t>
+  </si>
+  <si>
+    <t>zib2020</t>
+  </si>
+  <si>
+    <t>Behandelaanwijzing2</t>
   </si>
 </sst>
 </file>
@@ -1998,14 +2007,49 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="13">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2029,21 +2073,6 @@
           <bgColor theme="4" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
@@ -6267,14 +6296,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{4E88AAA9-DEAA-E34D-87AB-F7D1E6EF06F6}" name="Table3" displayName="Table3" ref="A1:G2" totalsRowShown="0" dataDxfId="11" tableBorderDxfId="10">
-  <autoFilter ref="A1:G2" xr:uid="{4E88AAA9-DEAA-E34D-87AB-F7D1E6EF06F6}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{F516092D-0429-7942-87B4-44E30560F822}" name="zib" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{DF0D7777-1AE4-0B4E-B735-827CF4661A7D}" name="wiki_URL_2020" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{3A52A617-1DD2-B642-9F68-B263734D9BB4}" name="wiki_URL_2017" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{C9C089A8-81ED-4145-A5C2-F010054C8043}" name="OID_zib2020" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{9DEADF10-D96C-4185-8725-608C24785C16}" name="OID_zib2017" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{4E88AAA9-DEAA-E34D-87AB-F7D1E6EF06F6}" name="Table3" displayName="Table3" ref="A1:H2" totalsRowShown="0" dataDxfId="12" tableBorderDxfId="11">
+  <autoFilter ref="A1:H2" xr:uid="{4E88AAA9-DEAA-E34D-87AB-F7D1E6EF06F6}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{F516092D-0429-7942-87B4-44E30560F822}" name="zib2017" dataDxfId="10"/>
+    <tableColumn id="8" xr3:uid="{6B2FB789-5823-4D1E-BBA9-BEBF19E185D5}" name="zib2020" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{DF0D7777-1AE4-0B4E-B735-827CF4661A7D}" name="wiki_URL_2020" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{3A52A617-1DD2-B642-9F68-B263734D9BB4}" name="wiki_URL_2017" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{C9C089A8-81ED-4145-A5C2-F010054C8043}" name="OID_zib2020" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{9DEADF10-D96C-4185-8725-608C24785C16}" name="OID_zib2017" dataDxfId="6"/>
     <tableColumn id="5" xr3:uid="{D3883306-50C2-BC4A-B7E3-158558CB0EAD}" name="sub_header_1"/>
     <tableColumn id="6" xr3:uid="{2569FBC5-AAE8-5646-9810-A5E2A3F41228}" name="sub_header_2"/>
   </tableColumns>
@@ -6644,58 +6674,64 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{190018DB-705B-1C49-8BBE-D7735C134696}">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.140625" customWidth="1"/>
-    <col min="2" max="2" width="41.28515625" customWidth="1"/>
-    <col min="3" max="3" width="48.85546875" customWidth="1"/>
-    <col min="4" max="5" width="35.42578125" customWidth="1"/>
-    <col min="6" max="6" width="67.42578125" style="5" customWidth="1"/>
-    <col min="7" max="7" width="71.42578125" style="5" customWidth="1"/>
+    <col min="1" max="2" width="22.109375" customWidth="1"/>
+    <col min="3" max="3" width="41.33203125" customWidth="1"/>
+    <col min="4" max="4" width="48.88671875" customWidth="1"/>
+    <col min="5" max="6" width="35.44140625" customWidth="1"/>
+    <col min="7" max="7" width="67.44140625" style="5" customWidth="1"/>
+    <col min="8" max="8" width="71.44140625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
-        <v>0</v>
+        <v>612</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>613</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>606</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>605</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="E1" s="10" t="s">
         <v>611</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="F1" s="10" t="s">
         <v>610</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="G1" s="11" t="s">
         <v>607</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>608</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>609</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="12" t="s">
+        <v>614</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="D2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="E2" s="12" t="s">
         <v>372</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="F2" s="13" t="s">
         <v>369</v>
       </c>
-      <c r="F2" s="11"/>
-      <c r="G2" s="6"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6708,1643 +6744,1643 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BCFD827-7ADE-CC42-A664-40C1A9F4F2E3}">
   <dimension ref="A3:A329"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="68.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="68.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>601</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A181" s="4" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A183" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A185" s="4" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A194" s="3" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A197" s="3" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A199" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A200" s="3" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A201" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A203" s="3" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A205" s="3" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A207" s="4" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A208" s="3" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A209" s="4" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A211" s="3" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A213" s="4" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A214" s="3" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A215" s="4" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A217" s="3" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A219" s="3" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A221" s="4" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A222" s="3" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A223" s="4" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A225" s="3" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A227" s="4" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A228" s="3" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A229" s="4" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A231" s="3" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="233" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A233" s="4" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="234" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A234" s="3" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A235" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="236" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="237" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A237" s="3" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="238" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="239" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A239" s="4" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="240" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A240" s="3" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="241" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A241" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="242" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A242" s="3" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="243" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A243" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="244" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A244" s="4" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="245" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A245" s="3" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="246" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A246" s="4" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="247" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A247" s="4" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="248" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A248" s="3" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="249" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A249" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="250" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A250" s="4" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="251" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A251" s="3" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="252" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A252" s="4" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="253" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A253" s="4" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="254" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A254" s="3" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="255" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A255" s="4" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="256" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A256" s="4" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="257" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A257" s="3" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="258" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A258" s="4" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="259" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A259" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="260" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A260" s="3" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="261" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A261" s="4" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="262" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A262" s="4" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="263" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A263" s="3" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="264" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A264" s="4" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="265" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A265" s="4" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="266" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A266" s="3" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="267" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A267" s="4" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="268" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A268" s="4" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="269" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A269" s="3" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="270" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A270" s="4" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="271" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A271" s="4" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="272" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A272" s="3" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="273" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A273" s="4" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="274" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A274" s="4" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="275" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A275" s="3" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="276" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A276" s="4" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="277" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A277" s="4" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="278" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A278" s="3" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="279" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A279" s="4" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="280" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A280" s="4" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="281" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A281" s="3" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="282" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A282" s="4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="283" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A283" s="4" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="284" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A284" s="3" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="285" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A285" s="4" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="286" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A286" s="4" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="287" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A287" s="3" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="288" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A288" s="4" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="289" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A289" s="3" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="290" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A290" s="4" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="291" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A291" s="4" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="292" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A292" s="3" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="293" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A293" s="4" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="294" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A294" s="4" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="295" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A295" s="3" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="296" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A296" s="4" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="297" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A297" s="4" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="298" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A298" s="3" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="299" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A299" s="4" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="300" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A300" s="3" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="301" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A301" s="4" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="302" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A302" s="3" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="303" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A303" s="4" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="304" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A304" s="4" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="305" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A305" s="3" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="306" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A306" s="4" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="307" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A307" s="4" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="308" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A308" s="3" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="309" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A309" s="4" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="310" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A310" s="4" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="311" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A311" s="3" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="312" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A312" s="4" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="313" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A313" s="4" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="314" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A314" s="3" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="315" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A315" s="4" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="316" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A316" s="4" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="317" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A317" s="3" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="318" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A318" s="4" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="319" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A319" s="3" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="320" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A320" s="4" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="321" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A321" s="3" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="322" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A322" s="4" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="323" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A323" s="3" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="324" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A324" s="4" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="325" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A325" s="4" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="326" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A326" s="3" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="327" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A327" s="4" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="328" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A328" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="329" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A329" s="3" t="s">
         <v>602</v>
       </c>
@@ -8357,18 +8393,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD818E27-D014-A348-BCE0-0E812E70AA74}">
   <dimension ref="A1:J211"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.140625" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
-    <col min="4" max="5" width="11.42578125" customWidth="1"/>
+    <col min="1" max="1" width="22.109375" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" customWidth="1"/>
+    <col min="3" max="3" width="17.109375" customWidth="1"/>
+    <col min="4" max="5" width="11.44140625" customWidth="1"/>
     <col min="6" max="6" width="54" customWidth="1"/>
     <col min="8" max="8" width="32" customWidth="1"/>
-    <col min="10" max="10" width="21.42578125" customWidth="1"/>
+    <col min="10" max="10" width="21.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8400,7 +8436,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>277</v>
       </c>
@@ -8426,7 +8462,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>277</v>
       </c>
@@ -8455,7 +8491,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>383</v>
       </c>
@@ -8481,7 +8517,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>383</v>
       </c>
@@ -8510,7 +8546,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>506</v>
       </c>
@@ -8536,7 +8572,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>506</v>
       </c>
@@ -8565,7 +8601,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>524</v>
       </c>
@@ -8591,7 +8627,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>524</v>
       </c>
@@ -8620,7 +8656,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>298</v>
       </c>
@@ -8646,7 +8682,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>527</v>
       </c>
@@ -8675,7 +8711,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>527</v>
       </c>
@@ -8701,7 +8737,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>389</v>
       </c>
@@ -8730,7 +8766,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>249</v>
       </c>
@@ -8759,7 +8795,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>249</v>
       </c>
@@ -8785,7 +8821,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>420</v>
       </c>
@@ -8811,7 +8847,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>420</v>
       </c>
@@ -8840,7 +8876,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>202</v>
       </c>
@@ -8869,7 +8905,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>368</v>
       </c>
@@ -8898,7 +8934,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>371</v>
       </c>
@@ -8927,7 +8963,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>304</v>
       </c>
@@ -8953,7 +8989,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>304</v>
       </c>
@@ -8982,7 +9018,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>374</v>
       </c>
@@ -9011,7 +9047,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>374</v>
       </c>
@@ -9037,7 +9073,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>212</v>
       </c>
@@ -9066,7 +9102,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>212</v>
       </c>
@@ -9092,7 +9128,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>408</v>
       </c>
@@ -9118,7 +9154,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>408</v>
       </c>
@@ -9147,7 +9183,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>274</v>
       </c>
@@ -9173,7 +9209,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>274</v>
       </c>
@@ -9202,7 +9238,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>365</v>
       </c>
@@ -9228,7 +9264,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>365</v>
       </c>
@@ -9257,7 +9293,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>521</v>
       </c>
@@ -9283,7 +9319,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>521</v>
       </c>
@@ -9312,7 +9348,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>252</v>
       </c>
@@ -9338,7 +9374,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>252</v>
       </c>
@@ -9367,7 +9403,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>237</v>
       </c>
@@ -9393,7 +9429,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>237</v>
       </c>
@@ -9422,7 +9458,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>323</v>
       </c>
@@ -9448,7 +9484,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>323</v>
       </c>
@@ -9477,7 +9513,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>386</v>
       </c>
@@ -9503,7 +9539,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>386</v>
       </c>
@@ -9532,7 +9568,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>392</v>
       </c>
@@ -9558,7 +9594,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>392</v>
       </c>
@@ -9587,7 +9623,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>411</v>
       </c>
@@ -9616,7 +9652,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>411</v>
       </c>
@@ -9642,7 +9678,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>255</v>
       </c>
@@ -9671,7 +9707,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>356</v>
       </c>
@@ -9697,7 +9733,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>356</v>
       </c>
@@ -9726,7 +9762,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>353</v>
       </c>
@@ -9752,7 +9788,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>353</v>
       </c>
@@ -9781,7 +9817,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>509</v>
       </c>
@@ -9807,7 +9843,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>509</v>
       </c>
@@ -9836,7 +9872,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>476</v>
       </c>
@@ -9862,7 +9898,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>476</v>
       </c>
@@ -9891,7 +9927,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>551</v>
       </c>
@@ -9917,7 +9953,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>551</v>
       </c>
@@ -9946,7 +9982,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>240</v>
       </c>
@@ -9972,7 +10008,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>240</v>
       </c>
@@ -10001,7 +10037,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>417</v>
       </c>
@@ -10027,7 +10063,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>417</v>
       </c>
@@ -10056,7 +10092,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>414</v>
       </c>
@@ -10082,7 +10118,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>414</v>
       </c>
@@ -10111,7 +10147,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>426</v>
       </c>
@@ -10137,7 +10173,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>426</v>
       </c>
@@ -10166,7 +10202,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>537</v>
       </c>
@@ -10192,7 +10228,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>537</v>
       </c>
@@ -10221,7 +10257,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>488</v>
       </c>
@@ -10247,7 +10283,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>488</v>
       </c>
@@ -10276,7 +10312,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>497</v>
       </c>
@@ -10302,7 +10338,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>497</v>
       </c>
@@ -10331,7 +10367,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>286</v>
       </c>
@@ -10357,7 +10393,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>286</v>
       </c>
@@ -10386,7 +10422,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>271</v>
       </c>
@@ -10412,7 +10448,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>271</v>
       </c>
@@ -10441,7 +10477,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>362</v>
       </c>
@@ -10467,7 +10503,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>362</v>
       </c>
@@ -10496,7 +10532,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>395</v>
       </c>
@@ -10522,7 +10558,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>395</v>
       </c>
@@ -10551,7 +10587,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>218</v>
       </c>
@@ -10577,7 +10613,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>218</v>
       </c>
@@ -10606,7 +10642,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>500</v>
       </c>
@@ -10635,7 +10671,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>292</v>
       </c>
@@ -10661,7 +10697,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>292</v>
       </c>
@@ -10690,7 +10726,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>512</v>
       </c>
@@ -10716,7 +10752,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>512</v>
       </c>
@@ -10745,7 +10781,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>231</v>
       </c>
@@ -10771,7 +10807,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>231</v>
       </c>
@@ -10800,7 +10836,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>262</v>
       </c>
@@ -10829,7 +10865,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>262</v>
       </c>
@@ -10855,7 +10891,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>280</v>
       </c>
@@ -10884,7 +10920,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="92" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>280</v>
       </c>
@@ -10910,7 +10946,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>548</v>
       </c>
@@ -10936,7 +10972,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>548</v>
       </c>
@@ -10965,7 +11001,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>543</v>
       </c>
@@ -10994,7 +11030,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="96" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>534</v>
       </c>
@@ -11020,7 +11056,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="97" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>534</v>
       </c>
@@ -11049,7 +11085,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>540</v>
       </c>
@@ -11075,7 +11111,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>540</v>
       </c>
@@ -11104,7 +11140,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>556</v>
       </c>
@@ -11133,7 +11169,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>556</v>
       </c>
@@ -11159,7 +11195,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="102" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>215</v>
       </c>
@@ -11185,7 +11221,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="103" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>215</v>
       </c>
@@ -11214,7 +11250,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>438</v>
       </c>
@@ -11240,7 +11276,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>438</v>
       </c>
@@ -11269,7 +11305,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>460</v>
       </c>
@@ -11295,7 +11331,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>460</v>
       </c>
@@ -11324,7 +11360,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="108" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>380</v>
       </c>
@@ -11350,7 +11386,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="109" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>380</v>
       </c>
@@ -11379,7 +11415,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="110" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>515</v>
       </c>
@@ -11405,7 +11441,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>515</v>
       </c>
@@ -11434,7 +11470,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>234</v>
       </c>
@@ -11460,7 +11496,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>234</v>
       </c>
@@ -11489,7 +11525,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>447</v>
       </c>
@@ -11515,7 +11551,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>447</v>
       </c>
@@ -11544,7 +11580,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>479</v>
       </c>
@@ -11570,7 +11606,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>479</v>
       </c>
@@ -11599,7 +11635,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>329</v>
       </c>
@@ -11628,7 +11664,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>350</v>
       </c>
@@ -11654,7 +11690,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>350</v>
       </c>
@@ -11683,7 +11719,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>207</v>
       </c>
@@ -11709,7 +11745,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>207</v>
       </c>
@@ -11738,7 +11774,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>326</v>
       </c>
@@ -11764,7 +11800,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>268</v>
       </c>
@@ -11793,7 +11829,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>289</v>
       </c>
@@ -11819,7 +11855,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>289</v>
       </c>
@@ -11848,7 +11884,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>283</v>
       </c>
@@ -11874,7 +11910,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>283</v>
       </c>
@@ -11903,7 +11939,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="129" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>472</v>
       </c>
@@ -11929,7 +11965,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="130" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>472</v>
       </c>
@@ -11958,7 +11994,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="131" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>265</v>
       </c>
@@ -11987,7 +12023,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>243</v>
       </c>
@@ -12013,7 +12049,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="133" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>243</v>
       </c>
@@ -12042,7 +12078,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="134" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>441</v>
       </c>
@@ -12068,7 +12104,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="135" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>441</v>
       </c>
@@ -12097,7 +12133,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="136" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>435</v>
       </c>
@@ -12123,7 +12159,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="137" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>435</v>
       </c>
@@ -12152,7 +12188,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="138" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>463</v>
       </c>
@@ -12178,7 +12214,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="139" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>463</v>
       </c>
@@ -12207,7 +12243,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="140" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>307</v>
       </c>
@@ -12236,7 +12272,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="141" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>221</v>
       </c>
@@ -12262,7 +12298,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>221</v>
       </c>
@@ -12291,7 +12327,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="143" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>224</v>
       </c>
@@ -12317,7 +12353,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="144" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>224</v>
       </c>
@@ -12346,7 +12382,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="145" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>432</v>
       </c>
@@ -12372,7 +12408,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="146" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>432</v>
       </c>
@@ -12401,7 +12437,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="147" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>485</v>
       </c>
@@ -12427,7 +12463,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="148" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>485</v>
       </c>
@@ -12456,7 +12492,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="149" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>503</v>
       </c>
@@ -12482,7 +12518,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="150" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>503</v>
       </c>
@@ -12511,7 +12547,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="151" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>295</v>
       </c>
@@ -12537,7 +12573,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="152" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>295</v>
       </c>
@@ -12566,7 +12602,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="153" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>377</v>
       </c>
@@ -12592,7 +12628,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="154" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>377</v>
       </c>
@@ -12621,7 +12657,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="155" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>429</v>
       </c>
@@ -12650,7 +12686,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="156" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>554</v>
       </c>
@@ -12676,7 +12712,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="157" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>554</v>
       </c>
@@ -12705,7 +12741,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="158" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>301</v>
       </c>
@@ -12731,7 +12767,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="159" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>301</v>
       </c>
@@ -12760,7 +12796,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="160" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>228</v>
       </c>
@@ -12786,7 +12822,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="161" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>228</v>
       </c>
@@ -12815,7 +12851,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="162" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>469</v>
       </c>
@@ -12844,7 +12880,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="163" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>469</v>
       </c>
@@ -12870,7 +12906,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="164" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>466</v>
       </c>
@@ -12899,7 +12935,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="165" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>466</v>
       </c>
@@ -12925,7 +12961,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="166" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>405</v>
       </c>
@@ -12951,7 +12987,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="167" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>405</v>
       </c>
@@ -12980,7 +13016,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="168" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>423</v>
       </c>
@@ -13009,7 +13045,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="169" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>423</v>
       </c>
@@ -13035,7 +13071,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="170" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>450</v>
       </c>
@@ -13064,7 +13100,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="171" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>450</v>
       </c>
@@ -13090,7 +13126,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="172" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>453</v>
       </c>
@@ -13119,7 +13155,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="173" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>453</v>
       </c>
@@ -13145,7 +13181,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="174" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>456</v>
       </c>
@@ -13174,7 +13210,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="175" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>456</v>
       </c>
@@ -13200,7 +13236,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="176" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>402</v>
       </c>
@@ -13229,7 +13265,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="177" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>402</v>
       </c>
@@ -13255,7 +13291,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="178" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>399</v>
       </c>
@@ -13284,7 +13320,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="179" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>399</v>
       </c>
@@ -13310,7 +13346,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="180" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>314</v>
       </c>
@@ -13336,7 +13372,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="181" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>314</v>
       </c>
@@ -13365,7 +13401,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="182" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>311</v>
       </c>
@@ -13391,7 +13427,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="183" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>311</v>
       </c>
@@ -13420,7 +13456,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="184" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>530</v>
       </c>
@@ -13446,7 +13482,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="185" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>530</v>
       </c>
@@ -13475,7 +13511,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="186" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>259</v>
       </c>
@@ -13504,7 +13540,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="187" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>246</v>
       </c>
@@ -13533,7 +13569,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="188" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>246</v>
       </c>
@@ -13559,7 +13595,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="189" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>482</v>
       </c>
@@ -13585,7 +13621,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="190" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>482</v>
       </c>
@@ -13614,7 +13650,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="191" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>444</v>
       </c>
@@ -13640,7 +13676,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="192" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>444</v>
       </c>
@@ -13669,7 +13705,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="193" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>320</v>
       </c>
@@ -13698,7 +13734,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="194" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>317</v>
       </c>
@@ -13727,7 +13763,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="195" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>494</v>
       </c>
@@ -13756,7 +13792,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="196" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>494</v>
       </c>
@@ -13782,7 +13818,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="197" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>359</v>
       </c>
@@ -13808,7 +13844,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="198" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>359</v>
       </c>
@@ -13837,7 +13873,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="199" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>518</v>
       </c>
@@ -13863,7 +13899,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="200" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>518</v>
       </c>
@@ -13892,7 +13928,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="201" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>347</v>
       </c>
@@ -13918,7 +13954,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="202" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>347</v>
       </c>
@@ -13947,7 +13983,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="203" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>341</v>
       </c>
@@ -13973,7 +14009,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="204" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>341</v>
       </c>
@@ -14002,7 +14038,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="205" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>332</v>
       </c>
@@ -14031,7 +14067,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="206" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>335</v>
       </c>
@@ -14060,7 +14096,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="207" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>344</v>
       </c>
@@ -14089,7 +14125,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="208" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>338</v>
       </c>
@@ -14115,7 +14151,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="209" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>338</v>
       </c>
@@ -14144,7 +14180,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="210" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>491</v>
       </c>
@@ -14170,7 +14206,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="211" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>491</v>
       </c>
@@ -14213,14 +14249,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBF75645-D2C8-D54C-989B-0700AFD1F77D}">
   <dimension ref="A1:E116"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="25.7109375" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" customWidth="1"/>
-    <col min="4" max="4" width="30.140625" customWidth="1"/>
+    <col min="1" max="2" width="25.6640625" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" customWidth="1"/>
+    <col min="4" max="4" width="30.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -14237,7 +14273,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>202</v>
       </c>
@@ -14251,7 +14287,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>207</v>
       </c>
@@ -14265,7 +14301,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>212</v>
       </c>
@@ -14282,7 +14318,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>215</v>
       </c>
@@ -14296,7 +14332,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>218</v>
       </c>
@@ -14310,7 +14346,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>221</v>
       </c>
@@ -14324,7 +14360,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>224</v>
       </c>
@@ -14338,7 +14374,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>228</v>
       </c>
@@ -14352,7 +14388,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>231</v>
       </c>
@@ -14366,7 +14402,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>234</v>
       </c>
@@ -14380,7 +14416,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>237</v>
       </c>
@@ -14394,7 +14430,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>240</v>
       </c>
@@ -14408,7 +14444,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>243</v>
       </c>
@@ -14422,7 +14458,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>246</v>
       </c>
@@ -14436,7 +14472,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>249</v>
       </c>
@@ -14450,7 +14486,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>252</v>
       </c>
@@ -14464,7 +14500,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>255</v>
       </c>
@@ -14478,7 +14514,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>259</v>
       </c>
@@ -14492,7 +14528,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>262</v>
       </c>
@@ -14506,7 +14542,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>265</v>
       </c>
@@ -14520,7 +14556,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>268</v>
       </c>
@@ -14534,7 +14570,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>271</v>
       </c>
@@ -14548,7 +14584,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>274</v>
       </c>
@@ -14562,7 +14598,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>277</v>
       </c>
@@ -14576,7 +14612,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>280</v>
       </c>
@@ -14590,7 +14626,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>283</v>
       </c>
@@ -14604,7 +14640,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>286</v>
       </c>
@@ -14618,7 +14654,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>289</v>
       </c>
@@ -14632,7 +14668,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>292</v>
       </c>
@@ -14646,7 +14682,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>295</v>
       </c>
@@ -14660,7 +14696,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>298</v>
       </c>
@@ -14674,7 +14710,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>301</v>
       </c>
@@ -14688,7 +14724,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>304</v>
       </c>
@@ -14702,7 +14738,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>307</v>
       </c>
@@ -14716,7 +14752,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>311</v>
       </c>
@@ -14730,7 +14766,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>314</v>
       </c>
@@ -14744,7 +14780,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>317</v>
       </c>
@@ -14758,7 +14794,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>320</v>
       </c>
@@ -14772,7 +14808,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>323</v>
       </c>
@@ -14786,7 +14822,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>326</v>
       </c>
@@ -14800,7 +14836,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>329</v>
       </c>
@@ -14814,7 +14850,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>332</v>
       </c>
@@ -14828,7 +14864,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>335</v>
       </c>
@@ -14842,7 +14878,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>338</v>
       </c>
@@ -14856,7 +14892,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>341</v>
       </c>
@@ -14870,7 +14906,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>344</v>
       </c>
@@ -14884,7 +14920,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>347</v>
       </c>
@@ -14898,7 +14934,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>350</v>
       </c>
@@ -14912,7 +14948,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>353</v>
       </c>
@@ -14926,7 +14962,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>356</v>
       </c>
@@ -14940,7 +14976,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>359</v>
       </c>
@@ -14954,7 +14990,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>362</v>
       </c>
@@ -14968,7 +15004,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>365</v>
       </c>
@@ -14982,7 +15018,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>368</v>
       </c>
@@ -14996,7 +15032,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>371</v>
       </c>
@@ -15010,7 +15046,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>374</v>
       </c>
@@ -15024,7 +15060,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>377</v>
       </c>
@@ -15038,7 +15074,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>380</v>
       </c>
@@ -15052,7 +15088,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>383</v>
       </c>
@@ -15066,7 +15102,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>386</v>
       </c>
@@ -15080,7 +15116,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>389</v>
       </c>
@@ -15094,7 +15130,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>392</v>
       </c>
@@ -15108,7 +15144,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>395</v>
       </c>
@@ -15122,7 +15158,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>399</v>
       </c>
@@ -15136,7 +15172,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>402</v>
       </c>
@@ -15150,7 +15186,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>405</v>
       </c>
@@ -15164,7 +15200,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>408</v>
       </c>
@@ -15178,7 +15214,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>411</v>
       </c>
@@ -15192,7 +15228,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>414</v>
       </c>
@@ -15206,7 +15242,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>417</v>
       </c>
@@ -15220,7 +15256,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>420</v>
       </c>
@@ -15234,7 +15270,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>423</v>
       </c>
@@ -15248,7 +15284,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>426</v>
       </c>
@@ -15262,7 +15298,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>429</v>
       </c>
@@ -15276,7 +15312,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>432</v>
       </c>
@@ -15290,7 +15326,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>435</v>
       </c>
@@ -15304,7 +15340,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>438</v>
       </c>
@@ -15318,7 +15354,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>441</v>
       </c>
@@ -15332,7 +15368,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>444</v>
       </c>
@@ -15346,7 +15382,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>447</v>
       </c>
@@ -15360,7 +15396,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>450</v>
       </c>
@@ -15374,7 +15410,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>453</v>
       </c>
@@ -15388,7 +15424,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>456</v>
       </c>
@@ -15402,7 +15438,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>460</v>
       </c>
@@ -15416,7 +15452,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>463</v>
       </c>
@@ -15430,7 +15466,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>466</v>
       </c>
@@ -15444,7 +15480,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>469</v>
       </c>
@@ -15458,7 +15494,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>472</v>
       </c>
@@ -15472,7 +15508,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>476</v>
       </c>
@@ -15486,7 +15522,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>479</v>
       </c>
@@ -15500,7 +15536,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>482</v>
       </c>
@@ -15514,7 +15550,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>485</v>
       </c>
@@ -15528,7 +15564,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>488</v>
       </c>
@@ -15542,7 +15578,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>491</v>
       </c>
@@ -15556,7 +15592,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>494</v>
       </c>
@@ -15570,7 +15606,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>497</v>
       </c>
@@ -15584,7 +15620,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>500</v>
       </c>
@@ -15598,7 +15634,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>503</v>
       </c>
@@ -15612,7 +15648,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>506</v>
       </c>
@@ -15626,7 +15662,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>509</v>
       </c>
@@ -15640,7 +15676,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>512</v>
       </c>
@@ -15654,7 +15690,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>515</v>
       </c>
@@ -15668,7 +15704,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>518</v>
       </c>
@@ -15682,7 +15718,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>521</v>
       </c>
@@ -15696,7 +15732,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>524</v>
       </c>
@@ -15710,7 +15746,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>527</v>
       </c>
@@ -15724,7 +15760,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>530</v>
       </c>
@@ -15738,7 +15774,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>534</v>
       </c>
@@ -15752,7 +15788,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>537</v>
       </c>
@@ -15766,7 +15802,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>540</v>
       </c>
@@ -15780,7 +15816,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>543</v>
       </c>
@@ -15794,7 +15830,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>556</v>
       </c>
@@ -15808,7 +15844,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>548</v>
       </c>
@@ -15822,7 +15858,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>551</v>
       </c>
@@ -15836,7 +15872,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>554</v>
       </c>
